--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/demo-local/test_next/movie-blog-next15/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DDCCD5-C6C5-C745-8313-96472ED3A88C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFE1E7A-4D63-E946-89B3-7CC41C707CC3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="114">
   <si>
     <t>id</t>
   </si>
@@ -225,6 +225,144 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=BqFEVNjvZEo&amp;list=PLQr28Iyd9Bt0&amp;index=5&amp;pp=iAQB</t>
+  </si>
+  <si>
+    <t>phim-006</t>
+  </si>
+  <si>
+    <t>coc-tu-bat-tu</t>
+  </si>
+  <si>
+    <t>Cóc tu bất tử</t>
+  </si>
+  <si>
+    <t>/uploads/coc-tu-bat-tu.png</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IDwsWErqOkk?si=ZwYZLA33Og7eVpNR</t>
+  </si>
+  <si>
+    <t>https://youtu.be/8lh359TIbqM?si=Kz09qktwTIU1wHyp</t>
+  </si>
+  <si>
+    <t>https://youtu.be/C5whk5pHnSg?si=h78zAHJh4C7oYBUZ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9Xymh4osG70?si=6JyyexQumJn0DVW5</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OYn6kgjxTc4?si=9QR9xgqGllNkoFcw</t>
+  </si>
+  <si>
+    <t>Tập 7</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WwDf3oMqEJc?si=XF1SfMrpJOxgirVu</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FhsCijvHXcA?si=arIYcunwhHkKulMd</t>
+  </si>
+  <si>
+    <t>ep-009</t>
+  </si>
+  <si>
+    <t>Tập 9</t>
+  </si>
+  <si>
+    <t>ep-010</t>
+  </si>
+  <si>
+    <t>Tập 10</t>
+  </si>
+  <si>
+    <t>ep-011</t>
+  </si>
+  <si>
+    <t>Tập 11</t>
+  </si>
+  <si>
+    <t>ep-012</t>
+  </si>
+  <si>
+    <t>Tập 12</t>
+  </si>
+  <si>
+    <t>ep-013</t>
+  </si>
+  <si>
+    <t>Tập 13</t>
+  </si>
+  <si>
+    <t>ep-014</t>
+  </si>
+  <si>
+    <t>Tập 14</t>
+  </si>
+  <si>
+    <t>ep-015</t>
+  </si>
+  <si>
+    <t>Tập 15</t>
+  </si>
+  <si>
+    <t>ep-016</t>
+  </si>
+  <si>
+    <t>Tập 16</t>
+  </si>
+  <si>
+    <t>ep-017</t>
+  </si>
+  <si>
+    <t>Tập 17</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Eg15R58W6/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18Avwtc7XK/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19iWDLZqQL/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18CPo8KVf2/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/187Bin9b96/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EPXGcKLV7/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19EdmJPKQs/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1CRXgJpCDc/</t>
+  </si>
+  <si>
+    <t>ep-018</t>
+  </si>
+  <si>
+    <t>Tập 18</t>
+  </si>
+  <si>
+    <t>ep-019</t>
+  </si>
+  <si>
+    <t>Tập 19</t>
+  </si>
+  <si>
+    <t>ep-020</t>
+  </si>
+  <si>
+    <t>Tập 20</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18rFmQ7dAR/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1dHe32iMgg/</t>
   </si>
 </sst>
 </file>
@@ -307,7 +445,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MoviesTable" displayName="MoviesTable" ref="A1:F6" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MoviesTable" displayName="MoviesTable" ref="A1:F7" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="slug"/>
@@ -321,7 +459,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="EpisodesTable" displayName="EpisodesTable" ref="A1:F19" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="EpisodesTable" displayName="EpisodesTable" ref="A1:F38" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="movie_id"/>
@@ -529,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -653,6 +791,23 @@
         <v>49</v>
       </c>
     </row>
+    <row r="7" spans="1:6" ht="16">
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -663,14 +818,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1054,10 +1209,386 @@
         <v>31</v>
       </c>
     </row>
+    <row r="20" spans="1:6" ht="16">
+      <c r="A20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16">
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16">
+      <c r="A23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16">
+      <c r="A24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="16">
+      <c r="A25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="16">
+      <c r="A26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="16">
+      <c r="A27" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="16">
+      <c r="A28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="16">
+      <c r="A29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16">
+      <c r="A30" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="16">
+      <c r="A31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="16">
+      <c r="A32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="16">
+      <c r="A33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="16">
+      <c r="A34" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="16">
+      <c r="A35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="16">
+      <c r="A36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="16">
+      <c r="A37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16">
+      <c r="A38" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F2:F506" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="F2:F521" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"youtube,facebook,tiktok"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1072,10 +1603,19 @@
     <hyperlink ref="E17" r:id="rId8" xr:uid="{C1A0A02A-7231-8147-BF99-44DA0A1174E8}"/>
     <hyperlink ref="E18" r:id="rId9" xr:uid="{E2567D1A-F12E-E049-AC1D-0ECD9AF8A355}"/>
     <hyperlink ref="E19" r:id="rId10" xr:uid="{3E2C6CB6-21C5-AC46-965B-507C073D1461}"/>
+    <hyperlink ref="E20" r:id="rId11" xr:uid="{8192D828-5CB5-7F4B-A28A-92E79DC5F06D}"/>
+    <hyperlink ref="E21" r:id="rId12" xr:uid="{D5BCD001-C644-DC41-A171-A8BE5912CE5A}"/>
+    <hyperlink ref="E22" r:id="rId13" xr:uid="{6E150794-09B1-644A-9D10-A30648386284}"/>
+    <hyperlink ref="E23" r:id="rId14" xr:uid="{C9A7362C-16C6-2A40-9FDB-2D4DA9EAFEF8}"/>
+    <hyperlink ref="E24" r:id="rId15" xr:uid="{36001D6A-639F-5E44-800A-B9771D982404}"/>
+    <hyperlink ref="E25" r:id="rId16" xr:uid="{B621FBC1-5A4E-1F41-859B-062A68385D6F}"/>
+    <hyperlink ref="E26" r:id="rId17" xr:uid="{7B820316-63BD-664C-8DA3-A363EB321157}"/>
+    <hyperlink ref="E27" r:id="rId18" xr:uid="{F26279A0-952F-3441-BB6D-920C4AF26D38}"/>
+    <hyperlink ref="E28" r:id="rId19" xr:uid="{47992B5B-6F2F-934B-A672-5138B8296442}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId20"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFE1E7A-4D63-E946-89B3-7CC41C707CC3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D7BD2D-6711-DC42-A742-F55214BD0DC2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="147">
   <si>
     <t>id</t>
   </si>
@@ -363,6 +363,105 @@
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1dHe32iMgg/</t>
+  </si>
+  <si>
+    <t>phim-007</t>
+  </si>
+  <si>
+    <t>phim-008</t>
+  </si>
+  <si>
+    <t>phim-009</t>
+  </si>
+  <si>
+    <t>phim-010</t>
+  </si>
+  <si>
+    <t>phim-011</t>
+  </si>
+  <si>
+    <t>phim-012</t>
+  </si>
+  <si>
+    <t>phim-013</t>
+  </si>
+  <si>
+    <t>phim-014</t>
+  </si>
+  <si>
+    <t>phim-015</t>
+  </si>
+  <si>
+    <t>phim-016</t>
+  </si>
+  <si>
+    <t>phim-017</t>
+  </si>
+  <si>
+    <t>phim-018</t>
+  </si>
+  <si>
+    <t>phim-019</t>
+  </si>
+  <si>
+    <t>phim-020</t>
+  </si>
+  <si>
+    <t>phim-021</t>
+  </si>
+  <si>
+    <t>phim-022</t>
+  </si>
+  <si>
+    <t>phim-023</t>
+  </si>
+  <si>
+    <t>muc-than-ky</t>
+  </si>
+  <si>
+    <t>Mục thần ký</t>
+  </si>
+  <si>
+    <t>/uploads/muc-than-ky.png</t>
+  </si>
+  <si>
+    <t>Hoạt hình 3D</t>
+  </si>
+  <si>
+    <t>Tập 87</t>
+  </si>
+  <si>
+    <t>Tập 88</t>
+  </si>
+  <si>
+    <t>Tập 89</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18QzaV8oTH/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19GBC3QkC4/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1BZXpWUwfJ/</t>
+  </si>
+  <si>
+    <t>ep-021</t>
+  </si>
+  <si>
+    <t>Tập 90</t>
+  </si>
+  <si>
+    <t>ep-022</t>
+  </si>
+  <si>
+    <t>Tập 91</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1GvYhzztSV/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19Pj269Ng5/</t>
   </si>
 </sst>
 </file>
@@ -445,7 +544,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MoviesTable" displayName="MoviesTable" ref="A1:F7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MoviesTable" displayName="MoviesTable" ref="A1:F24" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="slug"/>
@@ -459,7 +558,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="EpisodesTable" displayName="EpisodesTable" ref="A1:F38" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="EpisodesTable" displayName="EpisodesTable" ref="A1:F43" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="movie_id"/>
@@ -667,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -808,7 +907,153 @@
         <v>49</v>
       </c>
     </row>
+    <row r="8" spans="1:6" ht="16">
+      <c r="A8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16">
+      <c r="A9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16">
+      <c r="A10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16">
+      <c r="A11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16">
+      <c r="A12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16">
+      <c r="A13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="16">
+      <c r="A14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16">
+      <c r="A15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="16">
+      <c r="A16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16">
+      <c r="A17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="16">
+      <c r="A18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16">
+      <c r="A19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="16">
+      <c r="A20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16">
+      <c r="A21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16">
+      <c r="A22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16">
+      <c r="A23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16">
+      <c r="A24" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -818,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1237,7 +1482,7 @@
         <v>68</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>33</v>
@@ -1257,7 +1502,7 @@
         <v>68</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>37</v>
@@ -1277,7 +1522,7 @@
         <v>68</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>52</v>
@@ -1297,7 +1542,7 @@
         <v>68</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>54</v>
@@ -1317,7 +1562,7 @@
         <v>68</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>77</v>
@@ -1337,7 +1582,7 @@
         <v>68</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>55</v>
@@ -1357,7 +1602,7 @@
         <v>68</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>81</v>
@@ -1377,7 +1622,7 @@
         <v>68</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>83</v>
@@ -1397,7 +1642,7 @@
         <v>68</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>85</v>
@@ -1415,7 +1660,7 @@
         <v>68</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>87</v>
@@ -1435,7 +1680,7 @@
         <v>68</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>89</v>
@@ -1455,7 +1700,7 @@
         <v>68</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>91</v>
@@ -1475,7 +1720,7 @@
         <v>68</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>93</v>
@@ -1495,7 +1740,7 @@
         <v>68</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>95</v>
@@ -1515,7 +1760,7 @@
         <v>68</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>97</v>
@@ -1535,7 +1780,7 @@
         <v>68</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>107</v>
@@ -1555,7 +1800,7 @@
         <v>68</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>109</v>
@@ -1575,7 +1820,7 @@
         <v>68</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>111</v>
@@ -1585,10 +1830,110 @@
         <v>35</v>
       </c>
     </row>
+    <row r="39" spans="1:6" ht="16">
+      <c r="A39" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39">
+        <v>87</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="16">
+      <c r="A40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40">
+        <v>88</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="16">
+      <c r="A41" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41">
+        <v>89</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="16">
+      <c r="A42" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42">
+        <v>90</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="16">
+      <c r="A43" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43">
+        <v>91</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F2:F521" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="F2:F523" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"youtube,facebook,tiktok"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D7BD2D-6711-DC42-A742-F55214BD0DC2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403168B1-34F3-994B-8B5A-CD87FD169976}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="150">
   <si>
     <t>id</t>
   </si>
@@ -446,15 +446,9 @@
     <t>https://www.facebook.com/share/v/1BZXpWUwfJ/</t>
   </si>
   <si>
-    <t>ep-021</t>
-  </si>
-  <si>
     <t>Tập 90</t>
   </si>
   <si>
-    <t>ep-022</t>
-  </si>
-  <si>
     <t>Tập 91</t>
   </si>
   <si>
@@ -462,6 +456,21 @@
   </si>
   <si>
     <t>https://www.facebook.com/share/v/19Pj269Ng5/</t>
+  </si>
+  <si>
+    <t>ep-087</t>
+  </si>
+  <si>
+    <t>ep-088</t>
+  </si>
+  <si>
+    <t>ep-089</t>
+  </si>
+  <si>
+    <t>ep-090</t>
+  </si>
+  <si>
+    <t>ep-091</t>
   </si>
 </sst>
 </file>
@@ -558,7 +567,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="EpisodesTable" displayName="EpisodesTable" ref="A1:F43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="EpisodesTable" displayName="EpisodesTable" ref="A1:F44" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="movie_id"/>
@@ -1063,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1832,7 +1841,7 @@
     </row>
     <row r="39" spans="1:6" ht="16">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>114</v>
@@ -1852,7 +1861,7 @@
     </row>
     <row r="40" spans="1:6" ht="16">
       <c r="A40" s="2" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>114</v>
@@ -1872,7 +1881,7 @@
     </row>
     <row r="41" spans="1:6" ht="16">
       <c r="A41" s="2" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>114</v>
@@ -1892,7 +1901,7 @@
     </row>
     <row r="42" spans="1:6" ht="16">
       <c r="A42" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>114</v>
@@ -1901,10 +1910,10 @@
         <v>90</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>35</v>
@@ -1912,7 +1921,7 @@
     </row>
     <row r="43" spans="1:6" ht="16">
       <c r="A43" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>114</v>
@@ -1921,14 +1930,21 @@
         <v>91</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>35</v>
       </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403168B1-34F3-994B-8B5A-CD87FD169976}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B2BB95-0C8B-7541-8844-DA4F34E39FC9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="162">
   <si>
     <t>id</t>
   </si>
@@ -471,6 +471,42 @@
   </si>
   <si>
     <t>ep-091</t>
+  </si>
+  <si>
+    <t>Tập 28</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Dd2SEjF1r/</t>
+  </si>
+  <si>
+    <t>Tập 29</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DXUPRZjt2/</t>
+  </si>
+  <si>
+    <t>Tập 30</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/198T8Re5oN/</t>
+  </si>
+  <si>
+    <t>Tập 31</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18S15Tn6Wc/</t>
+  </si>
+  <si>
+    <t>Tập 32</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EZHH6zjqe/</t>
+  </si>
+  <si>
+    <t>Tập 37</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1G53EhEFiM/</t>
   </si>
 </sst>
 </file>
@@ -567,7 +603,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="EpisodesTable" displayName="EpisodesTable" ref="A1:F44" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="EpisodesTable" displayName="EpisodesTable" ref="A1:F45" totalsRowShown="0">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="movie_id"/>
@@ -1072,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1939,12 +1975,125 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="2"/>
+    <row r="44" spans="1:6" ht="16">
+      <c r="A44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44">
+        <v>28</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="16">
+      <c r="A45" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45">
+        <v>29</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="16">
+      <c r="A46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46">
+        <v>30</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="16">
+      <c r="A47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47">
+        <v>31</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="16">
+      <c r="A48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48">
+        <v>32</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="16">
+      <c r="A49" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49">
+        <v>37</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1973,10 +2122,11 @@
     <hyperlink ref="E26" r:id="rId17" xr:uid="{7B820316-63BD-664C-8DA3-A363EB321157}"/>
     <hyperlink ref="E27" r:id="rId18" xr:uid="{F26279A0-952F-3441-BB6D-920C4AF26D38}"/>
     <hyperlink ref="E28" r:id="rId19" xr:uid="{47992B5B-6F2F-934B-A672-5138B8296442}"/>
+    <hyperlink ref="E44" r:id="rId20" xr:uid="{F53770EE-7EA0-6443-B4FF-152B70DA0287}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId21"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B2BB95-0C8B-7541-8844-DA4F34E39FC9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58CD2BE-9EBF-7B41-A66D-AA23E20D79C7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B58CD2BE-9EBF-7B41-A66D-AA23E20D79C7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BF62A5-2181-0D40-8537-6C507A42607E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="181">
   <si>
     <t>id</t>
   </si>
@@ -507,6 +507,63 @@
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1G53EhEFiM/</t>
+  </si>
+  <si>
+    <t>Hướng dẫn nhặt rác ngoài hành tinh</t>
+  </si>
+  <si>
+    <t>huong-dan-nhat-rac-ngoai-hanh-tinh</t>
+  </si>
+  <si>
+    <t>/uploads/huong-dan-nhat-rac-ngoai-hanh-tinh.png</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1baZ2PzvAh/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EjpohezvZ/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19A6Hi7dfd/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/14kWHuLEA2B/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DKh878Cyt/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DcjJkMFMZ/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EhJALswQK/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1FG1AWaubY/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18v1buxyhj/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19SyFpU25A/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1AoZWAAKAs/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1E7XTxwsYu/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19AcdFm9N1/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1LWK7DtxMW/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1HgsDYmuFF/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1BtS61b2GY/</t>
   </si>
 </sst>
 </file>
@@ -815,8 +872,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
@@ -972,6 +1030,15 @@
     <row r="9" spans="1:6" ht="16">
       <c r="A9" s="2" t="s">
         <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" t="s">
+        <v>164</v>
       </c>
       <c r="F9" t="s">
         <v>49</v>
@@ -1108,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2092,6 +2159,326 @@
         <v>161</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="16">
+      <c r="A50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="16">
+      <c r="A51" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="16">
+      <c r="A52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="16">
+      <c r="A53" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53">
+        <v>4</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="16">
+      <c r="A54" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="16">
+      <c r="A55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55">
+        <v>6</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="16">
+      <c r="A56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56">
+        <v>7</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="16">
+      <c r="A57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="16">
+      <c r="A58" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="16">
+      <c r="A59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59">
+        <v>10</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="16">
+      <c r="A60" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60">
+        <v>11</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="16">
+      <c r="A61" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61">
+        <v>12</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="16">
+      <c r="A62" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C62">
+        <v>13</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="16">
+      <c r="A63" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C63">
+        <v>14</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="16">
+      <c r="A64" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64">
+        <v>15</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="16">
+      <c r="A65" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C65">
+        <v>16</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>35</v>
       </c>
     </row>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BF62A5-2181-0D40-8537-6C507A42607E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155FDB70-2551-5942-9C16-B55507202C6A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="195">
   <si>
     <t>id</t>
   </si>
@@ -564,6 +564,48 @@
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1BtS61b2GY/</t>
+  </si>
+  <si>
+    <t>Top Killer, Reverse Hunting</t>
+  </si>
+  <si>
+    <t>Phim Ai hành động</t>
+  </si>
+  <si>
+    <t>phim truyền hình ngắn hải ngoại</t>
+  </si>
+  <si>
+    <t>top-killer-reverse-hunting</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EapPm6noH/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1F82xLMi8e/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Eqxq3DXRd/</t>
+  </si>
+  <si>
+    <t>https://youtu.be/3b2RY0ck2Z0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zg3WHQyM2Lk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Rk7CmxVmrAU</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/17iHSwuENq/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DZf4Ytqrt/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/14jXjMGULJ3/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EFm84GofQ/</t>
   </si>
 </sst>
 </file>
@@ -1048,8 +1090,17 @@
       <c r="A10" s="2" t="s">
         <v>116</v>
       </c>
+      <c r="B10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" t="s">
+        <v>183</v>
+      </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
@@ -1175,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2481,6 +2532,213 @@
       <c r="F65" s="2" t="s">
         <v>35</v>
       </c>
+    </row>
+    <row r="66" spans="1:6" ht="16">
+      <c r="A66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="16">
+      <c r="A67" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="16">
+      <c r="A68" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="16">
+      <c r="A69" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C69">
+        <v>4</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="16">
+      <c r="A70" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C70">
+        <v>5</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="16">
+      <c r="A71" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C71">
+        <v>6</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="16">
+      <c r="A72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C72">
+        <v>7</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="16">
+      <c r="A73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C73">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="16">
+      <c r="A74" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C74">
+        <v>9</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="16">
+      <c r="A75" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C75">
+        <v>10</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155FDB70-2551-5942-9C16-B55507202C6A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C557E0EA-79A8-4448-93DF-3A88938BC6FC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2538,7 +2538,7 @@
         <v>28</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2558,7 +2558,7 @@
         <v>32</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -2578,7 +2578,7 @@
         <v>36</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68">
         <v>3</v>
@@ -2598,7 +2598,7 @@
         <v>40</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C69">
         <v>4</v>
@@ -2618,7 +2618,7 @@
         <v>41</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C70">
         <v>5</v>
@@ -2638,7 +2638,7 @@
         <v>42</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C71">
         <v>6</v>
@@ -2658,7 +2658,7 @@
         <v>43</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72">
         <v>7</v>
@@ -2678,7 +2678,7 @@
         <v>44</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73">
         <v>8</v>
@@ -2698,7 +2698,7 @@
         <v>80</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C74">
         <v>9</v>
@@ -2718,7 +2718,7 @@
         <v>82</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C75">
         <v>10</v>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C557E0EA-79A8-4448-93DF-3A88938BC6FC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAAF285-DCB0-C04F-94BC-6462B478755B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="movies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="196">
   <si>
     <t>id</t>
   </si>
@@ -572,9 +572,6 @@
     <t>Phim Ai hành động</t>
   </si>
   <si>
-    <t>phim truyền hình ngắn hải ngoại</t>
-  </si>
-  <si>
     <t>top-killer-reverse-hunting</t>
   </si>
   <si>
@@ -606,6 +603,12 @@
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1EFm84GofQ/</t>
+  </si>
+  <si>
+    <t>/uploads/top-killer-reverse-hunting</t>
+  </si>
+  <si>
+    <t>phim truyền hình ngắn hải ngoại "Top Killer, Reverse Hunting"!</t>
   </si>
 </sst>
 </file>
@@ -1091,13 +1094,16 @@
         <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
         <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>183</v>
+        <v>194</v>
+      </c>
+      <c r="E10" t="s">
+        <v>195</v>
       </c>
       <c r="F10" t="s">
         <v>182</v>
@@ -2547,7 +2553,7 @@
         <v>29</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>35</v>
@@ -2567,7 +2573,7 @@
         <v>33</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>35</v>
@@ -2587,7 +2593,7 @@
         <v>37</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>35</v>
@@ -2607,7 +2613,7 @@
         <v>52</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>31</v>
@@ -2627,7 +2633,7 @@
         <v>53</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>31</v>
@@ -2647,7 +2653,7 @@
         <v>54</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>31</v>
@@ -2667,7 +2673,7 @@
         <v>77</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>35</v>
@@ -2687,7 +2693,7 @@
         <v>55</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>35</v>
@@ -2707,7 +2713,7 @@
         <v>81</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>35</v>
@@ -2727,7 +2733,7 @@
         <v>83</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>35</v>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBAAF285-DCB0-C04F-94BC-6462B478755B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F760D6DD-5139-3A45-BF82-C76498C9859F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -605,10 +605,10 @@
     <t>https://www.facebook.com/share/v/1EFm84GofQ/</t>
   </si>
   <si>
-    <t>/uploads/top-killer-reverse-hunting</t>
-  </si>
-  <si>
     <t>phim truyền hình ngắn hải ngoại "Top Killer, Reverse Hunting"!</t>
+  </si>
+  <si>
+    <t>/uploads/top-killer-reverse-hunting.png</t>
   </si>
 </sst>
 </file>
@@ -1100,10 +1100,10 @@
         <v>181</v>
       </c>
       <c r="D10" t="s">
+        <v>195</v>
+      </c>
+      <c r="E10" t="s">
         <v>194</v>
-      </c>
-      <c r="E10" t="s">
-        <v>195</v>
       </c>
       <c r="F10" t="s">
         <v>182</v>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F760D6DD-5139-3A45-BF82-C76498C9859F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DA806B-39D8-DD4C-AEBD-A10461969A67}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="208">
   <si>
     <t>id</t>
   </si>
@@ -609,6 +609,42 @@
   </si>
   <si>
     <t>/uploads/top-killer-reverse-hunting.png</t>
+  </si>
+  <si>
+    <t>Du hành xuyên thế giới Dragon Ball</t>
+  </si>
+  <si>
+    <t>du-hanh-xuyen-the-gioi-dragon-ball</t>
+  </si>
+  <si>
+    <t>/uploads/du-hanh-xuyen-the-gioi-dragon-ball.png</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1BwQFV4ULy/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/14n1RKLwsLF/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EwFdYxMWJ/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19SxspAMUW/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EP2xG5uR6/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1CA5LwqQxC/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1LNmievHtZ/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1NCAMZZ2ro/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1J2oaXawDi/</t>
   </si>
 </sst>
 </file>
@@ -1113,6 +1149,15 @@
       <c r="A11" s="2" t="s">
         <v>117</v>
       </c>
+      <c r="B11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" t="s">
+        <v>198</v>
+      </c>
       <c r="F11" t="s">
         <v>49</v>
       </c>
@@ -1232,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2739,12 +2784,206 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="2"/>
+    <row r="76" spans="1:6" ht="16">
+      <c r="A76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="16">
+      <c r="A77" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="16">
+      <c r="A78" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="16">
+      <c r="A79" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C79">
+        <v>4</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="16">
+      <c r="A80" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C80">
+        <v>5</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="16">
+      <c r="A81" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81">
+        <v>6</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="16">
+      <c r="A82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C82">
+        <v>7</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="16">
+      <c r="A83" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="16">
+      <c r="A84" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C84">
+        <v>9</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="2"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="2"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -2774,10 +3013,11 @@
     <hyperlink ref="E27" r:id="rId18" xr:uid="{F26279A0-952F-3441-BB6D-920C4AF26D38}"/>
     <hyperlink ref="E28" r:id="rId19" xr:uid="{47992B5B-6F2F-934B-A672-5138B8296442}"/>
     <hyperlink ref="E44" r:id="rId20" xr:uid="{F53770EE-7EA0-6443-B4FF-152B70DA0287}"/>
+    <hyperlink ref="E76" r:id="rId21" xr:uid="{701F996D-B4B2-6B44-84F7-1D3A2FB1C103}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId21"/>
+    <tablePart r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DA806B-39D8-DD4C-AEBD-A10461969A67}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB843EC0-9EBB-DB49-B4F2-AF1BE7C83406}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="movies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="231">
   <si>
     <t>id</t>
   </si>
@@ -645,6 +645,75 @@
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1J2oaXawDi/</t>
+  </si>
+  <si>
+    <t>hinh-012</t>
+  </si>
+  <si>
+    <t>Siêu mẫu hàng đầu nước mỹ nhất quyết đòi cưới tôi</t>
+  </si>
+  <si>
+    <t>/uploads/hinh-012.png</t>
+  </si>
+  <si>
+    <t>hinh-013</t>
+  </si>
+  <si>
+    <t>Cậu bé giao hàng xuyên qua thế giới tu tiên và biến thành lợn</t>
+  </si>
+  <si>
+    <t>/uploads/hinh-013.png</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19CFA555J9/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1KEt5aHrWT/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EbgtZ5Z23/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19h32BwCvF/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/197fnytT76/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1MEFpjvQhX/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19gg7C11hE/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19U2E1Hkgc/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19ZVyEXyEi/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1E7Xf5pV5W/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Hgv9fTxes/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1D5qB3E1Xx/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DbwCRveh4/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EshWfNBuG/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DthLGAek2/</t>
+  </si>
+  <si>
+    <t>Tập 33</t>
+  </si>
+  <si>
+    <t>Tập 34</t>
   </si>
 </sst>
 </file>
@@ -1166,6 +1235,15 @@
       <c r="A12" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="B12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D12" t="s">
+        <v>210</v>
+      </c>
       <c r="F12" t="s">
         <v>49</v>
       </c>
@@ -1173,6 +1251,15 @@
     <row r="13" spans="1:6" ht="16">
       <c r="A13" s="2" t="s">
         <v>119</v>
+      </c>
+      <c r="B13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" t="s">
+        <v>213</v>
       </c>
       <c r="F13" t="s">
         <v>49</v>
@@ -1277,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2964,26 +3051,305 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="2"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="2"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="2"/>
+    <row r="85" spans="1:6" ht="16">
+      <c r="A85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="16">
+      <c r="A86" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="16">
+      <c r="A87" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="16">
+      <c r="A88" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C88">
+        <v>4</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="16">
+      <c r="A89" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C89">
+        <v>5</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="16">
+      <c r="A90" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C90">
+        <v>6</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="16">
+      <c r="A91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91">
+        <v>7</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="16">
+      <c r="A92" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C92">
+        <v>8</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="16">
+      <c r="A93" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93">
+        <v>9</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="16">
+      <c r="A94" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C94">
+        <v>10</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="16">
+      <c r="A95" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C95">
+        <v>11</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E95" t="s">
+        <v>224</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="16">
+      <c r="A96" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C96">
+        <v>12</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E96" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="16">
+      <c r="A97" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C97">
+        <v>30</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="16">
+      <c r="A98" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C98">
+        <v>33</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="16">
+      <c r="A99" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99">
+        <v>34</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB843EC0-9EBB-DB49-B4F2-AF1BE7C83406}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3505D445-998A-8640-A808-DDBECD2545D8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="movies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="267">
   <si>
     <t>id</t>
   </si>
@@ -647,18 +647,12 @@
     <t>https://www.facebook.com/share/v/1J2oaXawDi/</t>
   </si>
   <si>
-    <t>hinh-012</t>
-  </si>
-  <si>
     <t>Siêu mẫu hàng đầu nước mỹ nhất quyết đòi cưới tôi</t>
   </si>
   <si>
     <t>/uploads/hinh-012.png</t>
   </si>
   <si>
-    <t>hinh-013</t>
-  </si>
-  <si>
     <t>Cậu bé giao hàng xuyên qua thế giới tu tiên và biến thành lợn</t>
   </si>
   <si>
@@ -714,6 +708,120 @@
   </si>
   <si>
     <t>Tập 34</t>
+  </si>
+  <si>
+    <t>/uploads/hinh-014.png</t>
+  </si>
+  <si>
+    <t>hinh-017</t>
+  </si>
+  <si>
+    <t>hinh-018</t>
+  </si>
+  <si>
+    <t>hinh-019</t>
+  </si>
+  <si>
+    <t>hinh-020</t>
+  </si>
+  <si>
+    <t>hinh-021</t>
+  </si>
+  <si>
+    <t>hinh-022</t>
+  </si>
+  <si>
+    <t>hinh-023</t>
+  </si>
+  <si>
+    <t>hinh-024</t>
+  </si>
+  <si>
+    <t>Cố gái quê hương muốn được yêu</t>
+  </si>
+  <si>
+    <t>Người tu luyện phóng túng Chen Sheng</t>
+  </si>
+  <si>
+    <t>Trải nghiệm cuộc sống hàng ngày của người bán hàng từ góc nhìn thứ nhất</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1JeHRwUNG9/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EbPqWUNuj/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1HSAnsSo8C/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EpvnHjCid/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Ho3TbpUov/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1GTCkRiedn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18h2wjmMkw/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1FRd6vygcu/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18VbyPQfXp/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/193yKiXoZt/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Ey16ArVAg/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EU18NkGQc/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/16FfNeooPGL/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1D6ctszf6V/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1UWn9PZ5NN/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EmYGJBT24/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DSighvmpM/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/14ufvv6EPg8/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Jq1NziE5Q/</t>
+  </si>
+  <si>
+    <t>sieu-mau-hang-dau-nuoc-my-nhat-quyet-doi-cuoi-toi</t>
+  </si>
+  <si>
+    <t>cau-be-giao-hang-xuyen-qua-the-gioi-tu-tien-va-bien-thanh-lon</t>
+  </si>
+  <si>
+    <t>co-gai-que-huong-muon-duoc-yeu</t>
+  </si>
+  <si>
+    <t>nguoi-tu-luyen-phong-tung-chen-sheng</t>
+  </si>
+  <si>
+    <t>trai-nghiem-cuoc-song-hang-ngay-cua-nguoi-ban-hang-tu-goc-nhin-thu-nhat</t>
+  </si>
+  <si>
+    <t>/uploads/hinh-015.png</t>
+  </si>
+  <si>
+    <t>/uploads/hinh-016.png</t>
   </si>
 </sst>
 </file>
@@ -1236,13 +1344,13 @@
         <v>118</v>
       </c>
       <c r="B12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" t="s">
         <v>208</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>209</v>
-      </c>
-      <c r="D12" t="s">
-        <v>210</v>
       </c>
       <c r="F12" t="s">
         <v>49</v>
@@ -1253,13 +1361,13 @@
         <v>119</v>
       </c>
       <c r="B13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" t="s">
         <v>211</v>
-      </c>
-      <c r="C13" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" t="s">
-        <v>213</v>
       </c>
       <c r="F13" t="s">
         <v>49</v>
@@ -1269,6 +1377,15 @@
       <c r="A14" s="2" t="s">
         <v>120</v>
       </c>
+      <c r="B14" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" t="s">
+        <v>238</v>
+      </c>
+      <c r="D14" t="s">
+        <v>229</v>
+      </c>
       <c r="F14" t="s">
         <v>49</v>
       </c>
@@ -1277,6 +1394,15 @@
       <c r="A15" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="B15" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" t="s">
+        <v>265</v>
+      </c>
       <c r="F15" t="s">
         <v>49</v>
       </c>
@@ -1285,6 +1411,15 @@
       <c r="A16" s="2" t="s">
         <v>122</v>
       </c>
+      <c r="B16" t="s">
+        <v>264</v>
+      </c>
+      <c r="C16" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" t="s">
+        <v>266</v>
+      </c>
       <c r="F16" t="s">
         <v>49</v>
       </c>
@@ -1293,6 +1428,9 @@
       <c r="A17" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="B17" t="s">
+        <v>230</v>
+      </c>
       <c r="F17" t="s">
         <v>49</v>
       </c>
@@ -1301,6 +1439,9 @@
       <c r="A18" s="2" t="s">
         <v>124</v>
       </c>
+      <c r="B18" t="s">
+        <v>231</v>
+      </c>
       <c r="F18" t="s">
         <v>49</v>
       </c>
@@ -1309,6 +1450,9 @@
       <c r="A19" s="2" t="s">
         <v>125</v>
       </c>
+      <c r="B19" t="s">
+        <v>232</v>
+      </c>
       <c r="F19" t="s">
         <v>49</v>
       </c>
@@ -1317,6 +1461,9 @@
       <c r="A20" s="2" t="s">
         <v>126</v>
       </c>
+      <c r="B20" t="s">
+        <v>233</v>
+      </c>
       <c r="F20" t="s">
         <v>49</v>
       </c>
@@ -1325,6 +1472,9 @@
       <c r="A21" s="2" t="s">
         <v>127</v>
       </c>
+      <c r="B21" t="s">
+        <v>234</v>
+      </c>
       <c r="F21" t="s">
         <v>49</v>
       </c>
@@ -1333,6 +1483,9 @@
       <c r="A22" s="2" t="s">
         <v>128</v>
       </c>
+      <c r="B22" t="s">
+        <v>235</v>
+      </c>
       <c r="F22" t="s">
         <v>49</v>
       </c>
@@ -1341,6 +1494,9 @@
       <c r="A23" s="2" t="s">
         <v>129</v>
       </c>
+      <c r="B23" t="s">
+        <v>236</v>
+      </c>
       <c r="F23" t="s">
         <v>49</v>
       </c>
@@ -1348,6 +1504,9 @@
     <row r="24" spans="1:6" ht="16">
       <c r="A24" s="2" t="s">
         <v>130</v>
+      </c>
+      <c r="B24" t="s">
+        <v>237</v>
       </c>
       <c r="F24" t="s">
         <v>49</v>
@@ -1364,7 +1523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3065,7 +3224,7 @@
         <v>29</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>35</v>
@@ -3085,7 +3244,7 @@
         <v>33</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>35</v>
@@ -3105,7 +3264,7 @@
         <v>37</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>35</v>
@@ -3125,7 +3284,7 @@
         <v>52</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>35</v>
@@ -3145,7 +3304,7 @@
         <v>53</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>35</v>
@@ -3165,7 +3324,7 @@
         <v>54</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>35</v>
@@ -3185,7 +3344,7 @@
         <v>77</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>35</v>
@@ -3205,7 +3364,7 @@
         <v>55</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>35</v>
@@ -3225,7 +3384,7 @@
         <v>81</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>35</v>
@@ -3245,7 +3404,7 @@
         <v>83</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>35</v>
@@ -3265,7 +3424,7 @@
         <v>85</v>
       </c>
       <c r="E95" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>35</v>
@@ -3285,7 +3444,7 @@
         <v>87</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>35</v>
@@ -3305,7 +3464,7 @@
         <v>154</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>35</v>
@@ -3322,10 +3481,10 @@
         <v>33</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>35</v>
@@ -3342,12 +3501,410 @@
         <v>34</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F99" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="16">
+      <c r="A100" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="16">
+      <c r="A101" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C101">
+        <v>2</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="16">
+      <c r="A102" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C102">
+        <v>3</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="16">
+      <c r="A103" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C103">
+        <v>4</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="16">
+      <c r="A104" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C104">
+        <v>5</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="16">
+      <c r="A105" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C105">
+        <v>6</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="16">
+      <c r="A106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C106">
+        <v>7</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="16">
+      <c r="A107" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C107">
+        <v>8</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="16">
+      <c r="A108" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C108">
+        <v>9</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E108" t="s">
+        <v>249</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="16">
+      <c r="A109" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="16">
+      <c r="A110" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="16">
+      <c r="A111" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="16">
+      <c r="A112" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C112">
+        <v>3</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="16">
+      <c r="A113" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C113">
+        <v>4</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="16">
+      <c r="A114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C114">
+        <v>5</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="16">
+      <c r="A115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C115">
+        <v>6</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="16">
+      <c r="A116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C116">
+        <v>7</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="16">
+      <c r="A117" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C117">
+        <v>8</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="16">
+      <c r="A118" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C118">
+        <v>9</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E118" t="s">
+        <v>258</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="16">
+      <c r="A119" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C119">
+        <v>10</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E119" t="s">
+        <v>259</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>35</v>
       </c>
     </row>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/demo-local/test_sku/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3505D445-998A-8640-A808-DDBECD2545D8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE9F35D-1EBD-364C-BD3E-55AC5209ABDE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="movies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="275">
   <si>
     <t>id</t>
   </si>
@@ -713,30 +713,6 @@
     <t>/uploads/hinh-014.png</t>
   </si>
   <si>
-    <t>hinh-017</t>
-  </si>
-  <si>
-    <t>hinh-018</t>
-  </si>
-  <si>
-    <t>hinh-019</t>
-  </si>
-  <si>
-    <t>hinh-020</t>
-  </si>
-  <si>
-    <t>hinh-021</t>
-  </si>
-  <si>
-    <t>hinh-022</t>
-  </si>
-  <si>
-    <t>hinh-023</t>
-  </si>
-  <si>
-    <t>hinh-024</t>
-  </si>
-  <si>
     <t>Cố gái quê hương muốn được yêu</t>
   </si>
   <si>
@@ -822,6 +798,54 @@
   </si>
   <si>
     <t>/uploads/hinh-016.png</t>
+  </si>
+  <si>
+    <t>Tôi mở KTV ở Hàn Quốc</t>
+  </si>
+  <si>
+    <t>toi-mo-ktv-o-han-quoc</t>
+  </si>
+  <si>
+    <t>/uploads/hinh-017.png</t>
+  </si>
+  <si>
+    <t>Phim Ai xã hội</t>
+  </si>
+  <si>
+    <t>Nội dung gốc, hoàn toàn hư cấu</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DTSFASk83/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18KUombgN2/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EyuvdHnze/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/19CLbAAYBm/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1EbuoFcEWd/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/18BtLzQ5UQ/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1FnsMUEgyV/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1cM5Arxe8c/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Buy6LxqSA/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Hkrnd2RtP/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1BpoL9pWVA/</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1368,7 @@
         <v>118</v>
       </c>
       <c r="B12" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C12" t="s">
         <v>208</v>
@@ -1361,7 +1385,7 @@
         <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C13" t="s">
         <v>210</v>
@@ -1378,10 +1402,10 @@
         <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C14" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D14" t="s">
         <v>229</v>
@@ -1395,13 +1419,13 @@
         <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C15" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D15" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="F15" t="s">
         <v>49</v>
@@ -1412,13 +1436,13 @@
         <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F16" t="s">
         <v>49</v>
@@ -1429,7 +1453,16 @@
         <v>123</v>
       </c>
       <c r="B17" t="s">
-        <v>230</v>
+        <v>260</v>
+      </c>
+      <c r="C17" t="s">
+        <v>259</v>
+      </c>
+      <c r="D17" t="s">
+        <v>261</v>
+      </c>
+      <c r="E17" t="s">
+        <v>263</v>
       </c>
       <c r="F17" t="s">
         <v>49</v>
@@ -1439,20 +1472,14 @@
       <c r="A18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B18" t="s">
-        <v>231</v>
-      </c>
       <c r="F18" t="s">
-        <v>49</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16">
       <c r="A19" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B19" t="s">
-        <v>232</v>
-      </c>
       <c r="F19" t="s">
         <v>49</v>
       </c>
@@ -1461,9 +1488,6 @@
       <c r="A20" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B20" t="s">
-        <v>233</v>
-      </c>
       <c r="F20" t="s">
         <v>49</v>
       </c>
@@ -1472,9 +1496,6 @@
       <c r="A21" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B21" t="s">
-        <v>234</v>
-      </c>
       <c r="F21" t="s">
         <v>49</v>
       </c>
@@ -1483,9 +1504,6 @@
       <c r="A22" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B22" t="s">
-        <v>235</v>
-      </c>
       <c r="F22" t="s">
         <v>49</v>
       </c>
@@ -1494,9 +1512,6 @@
       <c r="A23" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B23" t="s">
-        <v>236</v>
-      </c>
       <c r="F23" t="s">
         <v>49</v>
       </c>
@@ -1504,9 +1519,6 @@
     <row r="24" spans="1:6" ht="16">
       <c r="A24" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="B24" t="s">
-        <v>237</v>
       </c>
       <c r="F24" t="s">
         <v>49</v>
@@ -1523,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3524,7 +3536,7 @@
         <v>29</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>35</v>
@@ -3544,7 +3556,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>35</v>
@@ -3564,7 +3576,7 @@
         <v>37</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>35</v>
@@ -3584,7 +3596,7 @@
         <v>52</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>35</v>
@@ -3604,7 +3616,7 @@
         <v>53</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>35</v>
@@ -3624,7 +3636,7 @@
         <v>54</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>35</v>
@@ -3644,7 +3656,7 @@
         <v>77</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>35</v>
@@ -3664,7 +3676,7 @@
         <v>55</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>35</v>
@@ -3684,7 +3696,7 @@
         <v>81</v>
       </c>
       <c r="E108" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>35</v>
@@ -3703,26 +3715,28 @@
       <c r="D109" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E109" s="3"/>
+      <c r="E109" s="3" t="s">
+        <v>264</v>
+      </c>
       <c r="F109" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="16">
       <c r="A110" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>35</v>
@@ -3730,19 +3744,19 @@
     </row>
     <row r="111" spans="1:6" ht="16">
       <c r="A111" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>35</v>
@@ -3750,19 +3764,19 @@
     </row>
     <row r="112" spans="1:6" ht="16">
       <c r="A112" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>35</v>
@@ -3770,19 +3784,19 @@
     </row>
     <row r="113" spans="1:6" ht="16">
       <c r="A113" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C113">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>35</v>
@@ -3790,19 +3804,19 @@
     </row>
     <row r="114" spans="1:6" ht="16">
       <c r="A114" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>35</v>
@@ -3810,19 +3824,19 @@
     </row>
     <row r="115" spans="1:6" ht="16">
       <c r="A115" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>35</v>
@@ -3830,19 +3844,19 @@
     </row>
     <row r="116" spans="1:6" ht="16">
       <c r="A116" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>35</v>
@@ -3850,19 +3864,19 @@
     </row>
     <row r="117" spans="1:6" ht="16">
       <c r="A117" s="2" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C117">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>257</v>
+        <v>81</v>
+      </c>
+      <c r="E117" t="s">
+        <v>272</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>35</v>
@@ -3870,19 +3884,19 @@
     </row>
     <row r="118" spans="1:6" ht="16">
       <c r="A118" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C118">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E118" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>35</v>
@@ -3890,28 +3904,282 @@
     </row>
     <row r="119" spans="1:6" ht="16">
       <c r="A119" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C119">
+        <v>11</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="16">
+      <c r="A120" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="16">
+      <c r="A121" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="16">
+      <c r="A122" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C122">
+        <v>3</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="16">
+      <c r="A123" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C123">
+        <v>4</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="16">
+      <c r="A124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C124">
+        <v>5</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="16">
+      <c r="A125" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C125">
+        <v>6</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="16">
+      <c r="A126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C126">
+        <v>7</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="16">
+      <c r="A127" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C127">
+        <v>8</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="16">
+      <c r="A128" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C128">
+        <v>9</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E128" t="s">
+        <v>250</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="16">
+      <c r="A129" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B129" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C119">
+      <c r="C129">
         <v>10</v>
       </c>
-      <c r="D119" s="2" t="s">
+      <c r="D129" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E119" t="s">
-        <v>259</v>
-      </c>
-      <c r="F119" s="2" t="s">
+      <c r="E129" t="s">
+        <v>251</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="16">
+      <c r="A130" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E130" s="3"/>
+      <c r="F130" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="16">
+      <c r="A131" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C131">
+        <v>2</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E131" s="3"/>
+      <c r="F131" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="16">
+      <c r="A132" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C132">
+        <v>3</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E132" s="3"/>
+      <c r="F132" s="2" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="F2:F523" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" sqref="F2:F132 F149:F522" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"youtube,facebook,tiktok"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/demo-local/test_sku/sku069/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE9F35D-1EBD-364C-BD3E-55AC5209ABDE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7594E9B-FA9C-254F-8D94-D3278A5B97D0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="movies" sheetId="1" r:id="rId1"/>
@@ -1465,7 +1465,7 @@
         <v>263</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16">

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7594E9B-FA9C-254F-8D94-D3278A5B97D0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC21DB1-A1DC-BA4A-B994-EF476F7B60D7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="movies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="279">
   <si>
     <t>id</t>
   </si>
@@ -846,6 +846,18 @@
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1BpoL9pWVA/</t>
+  </si>
+  <si>
+    <t>Tập 27 - 41</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1CPW8NSg4w/</t>
+  </si>
+  <si>
+    <t>Tập 42 - 52</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1Aio6dWTwT/</t>
   </si>
 </sst>
 </file>
@@ -4151,9 +4163,11 @@
         <v>2</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E131" s="3"/>
+        <v>275</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="F131" s="2" t="s">
         <v>35</v>
       </c>
@@ -4169,9 +4183,11 @@
         <v>3</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E132" s="3"/>
+        <v>277</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="F132" s="2" t="s">
         <v>35</v>
       </c>
@@ -4205,10 +4221,12 @@
     <hyperlink ref="E28" r:id="rId19" xr:uid="{47992B5B-6F2F-934B-A672-5138B8296442}"/>
     <hyperlink ref="E44" r:id="rId20" xr:uid="{F53770EE-7EA0-6443-B4FF-152B70DA0287}"/>
     <hyperlink ref="E76" r:id="rId21" xr:uid="{701F996D-B4B2-6B44-84F7-1D3A2FB1C103}"/>
+    <hyperlink ref="E131" r:id="rId22" xr:uid="{A480B2B7-EA1C-1E49-B9E7-E45DC4ED5EF4}"/>
+    <hyperlink ref="E132" r:id="rId23" xr:uid="{419AA0CA-5EA3-B440-990D-36D10CE41845}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId22"/>
+    <tablePart r:id="rId24"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC21DB1-A1DC-BA4A-B994-EF476F7B60D7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9A02D2-CF1A-2C4F-A536-2CFFE3DB4712}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="movies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="286">
   <si>
     <t>id</t>
   </si>
@@ -858,6 +858,27 @@
   </si>
   <si>
     <t>https://www.facebook.com/share/v/1Aio6dWTwT/</t>
+  </si>
+  <si>
+    <t>Cục Điều tra Đặc biệt Ba</t>
+  </si>
+  <si>
+    <t>/uploads/hinh-default.png</t>
+  </si>
+  <si>
+    <t>Nhóc, trả lại nữ hoàng cho chúng tôi</t>
+  </si>
+  <si>
+    <t>Wheat War</t>
+  </si>
+  <si>
+    <t>cuc-dieu-tra-dac-biet-ba</t>
+  </si>
+  <si>
+    <t>nhoc-tra-lai-nu-hoang-cho-chung-toi</t>
+  </si>
+  <si>
+    <t>wheat-war</t>
   </si>
 </sst>
 </file>
@@ -1484,6 +1505,15 @@
       <c r="A18" s="2" t="s">
         <v>124</v>
       </c>
+      <c r="B18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C18" t="s">
+        <v>279</v>
+      </c>
+      <c r="D18" t="s">
+        <v>280</v>
+      </c>
       <c r="F18" t="s">
         <v>262</v>
       </c>
@@ -1492,6 +1522,15 @@
       <c r="A19" s="2" t="s">
         <v>125</v>
       </c>
+      <c r="B19" t="s">
+        <v>284</v>
+      </c>
+      <c r="C19" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" t="s">
+        <v>280</v>
+      </c>
       <c r="F19" t="s">
         <v>49</v>
       </c>
@@ -1499,6 +1538,15 @@
     <row r="20" spans="1:6" ht="16">
       <c r="A20" s="2" t="s">
         <v>126</v>
+      </c>
+      <c r="B20" t="s">
+        <v>285</v>
+      </c>
+      <c r="C20" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" t="s">
+        <v>280</v>
       </c>
       <c r="F20" t="s">
         <v>49</v>

--- a/data/movies.xlsx
+++ b/data/movies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dattran/Documents/GitHub/sku069/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9A02D2-CF1A-2C4F-A536-2CFFE3DB4712}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F8C039-5978-A74B-87B1-84E5D53B27BD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="movies" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="290">
   <si>
     <t>id</t>
   </si>
@@ -879,6 +879,18 @@
   </si>
   <si>
     <t>wheat-war</t>
+  </si>
+  <si>
+    <t>Tập 1 - 23</t>
+  </si>
+  <si>
+    <t>Tập 53 - 57</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1CEbzboiX8/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/v/1DJsFig3Yc/</t>
   </si>
 </sst>
 </file>
@@ -1595,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4193,9 +4205,11 @@
         <v>1</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E130" s="3"/>
+        <v>286</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>289</v>
+      </c>
       <c r="F130" s="2" t="s">
         <v>35</v>
       </c>
@@ -4210,12 +4224,6 @@
       <c r="C131">
         <v>2</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>276</v>
-      </c>
       <c r="F131" s="2" t="s">
         <v>35</v>
       </c>
@@ -4231,19 +4239,59 @@
         <v>3</v>
       </c>
       <c r="D132" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="16">
+      <c r="A133" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C133">
+        <v>4</v>
+      </c>
+      <c r="D133" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E132" s="3" t="s">
+      <c r="E133" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F132" s="2" t="s">
+      <c r="F133" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="16">
+      <c r="A134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C134">
+        <v>5</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" sqref="F2:F132 F149:F522" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="F149:F522 F2:F134" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"youtube,facebook,tiktok"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4269,12 +4317,13 @@
     <hyperlink ref="E28" r:id="rId19" xr:uid="{47992B5B-6F2F-934B-A672-5138B8296442}"/>
     <hyperlink ref="E44" r:id="rId20" xr:uid="{F53770EE-7EA0-6443-B4FF-152B70DA0287}"/>
     <hyperlink ref="E76" r:id="rId21" xr:uid="{701F996D-B4B2-6B44-84F7-1D3A2FB1C103}"/>
-    <hyperlink ref="E131" r:id="rId22" xr:uid="{A480B2B7-EA1C-1E49-B9E7-E45DC4ED5EF4}"/>
-    <hyperlink ref="E132" r:id="rId23" xr:uid="{419AA0CA-5EA3-B440-990D-36D10CE41845}"/>
+    <hyperlink ref="E132" r:id="rId22" xr:uid="{A480B2B7-EA1C-1E49-B9E7-E45DC4ED5EF4}"/>
+    <hyperlink ref="E133" r:id="rId23" xr:uid="{419AA0CA-5EA3-B440-990D-36D10CE41845}"/>
+    <hyperlink ref="E134" r:id="rId24" xr:uid="{6FA821A3-4380-394A-94BC-0F04025F66BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId24"/>
+    <tablePart r:id="rId25"/>
   </tableParts>
 </worksheet>
 </file>